--- a/Unity/Assets/Config/Excel/Datas/StartConfig/RouterTest/StartProcessConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/StartConfig/RouterTest/StartProcessConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\ETPlus\Unity\Assets\Config\Excel\Datas\StartConfig\RouterTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ChangeConfig\RouterTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10321BA-A1DC-4502-A5F1-7D8474EF8595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AABF7F9-6DD3-482E-89BD-30ABF43E472B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="2265" windowWidth="20775" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StartProcessConfig" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -97,6 +97,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -139,15 +145,9 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyAlignment="1">
@@ -155,6 +155,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -463,150 +469,140 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <col min="2" max="4" width="12.625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="6"/>
-    </row>
-    <row r="2" spans="1:5" s="7" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:5" s="5" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" s="3" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="4"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="4">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="B4" s="7">
+        <v>1</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
         <v>20001</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+      <c r="B5" s="8">
         <v>2</v>
       </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4">
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
         <v>20002</v>
       </c>
     </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="8">
         <v>3</v>
       </c>
-      <c r="C6" s="4">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
         <v>20003</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="3">
+      <c r="B7" s="8">
         <v>4</v>
       </c>
-      <c r="C7" s="4">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="7">
         <v>20004</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+      <c r="B8" s="8">
         <v>5</v>
       </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="7">
         <v>20005</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+      <c r="B9" s="8">
         <v>6</v>
       </c>
-      <c r="C9" s="4">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="7">
         <v>20006</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
+      <c r="B10" s="8">
         <v>7</v>
       </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
         <v>20007</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D13" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>